--- a/dados/equipamentos_saude_niteroi.xlsx
+++ b/dados/equipamentos_saude_niteroi.xlsx
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Rua Teixeira de Freitas, s/nº – Fonseca</t>
+          <t>Rua Teixeira de Freitas, s/n, Fonseca, 24130-616</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6614,7 +6614,11 @@
           <t>24 horas</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2627-1535</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -6648,11 +6652,15 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Hospitais</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
+          <t>SMS Niterói – Hospitais; coordenadas/endereço: https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>-22.88082874299994</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>-43.07839598499993</v>
+      </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
           <t>0012599</t>
@@ -6670,7 +6678,7 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6695,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Avenida Machado, s/nº – Barreto</t>
+          <t>Avenida Machado, s/n, Barreto, 24111-000</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6695,7 +6703,11 @@
           <t>24 horas</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2620-3434</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Metropolitana II</t>
@@ -6729,11 +6741,15 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Hospitais</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
+          <t>SMS Niterói – Hospitais; coordenadas/endereço: https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>-22.86509366699994</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>-43.09469462199996</v>
+      </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
           <t>0012556</t>
@@ -6751,7 +6767,7 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6784,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rua Desembargador Athayde Parreira, nº 266 – Fátima</t>
+          <t>Rua Desembargador Athaíde Parreiras, 266, Bairro de Fátima, 24070-090</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6776,7 +6792,11 @@
           <t>24 horas</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2523-8702</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -6810,11 +6830,15 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Hospitais</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
+          <t>SMS Niterói – Hospitais; coordenadas/endereço: https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>-22.89562906799994</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>-43.11036819699996</v>
+      </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
           <t>0012513</t>
@@ -6832,7 +6856,7 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6873,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Estrada do Grota, s/nº – Jurujuba</t>
+          <t>Avenida Quintino Bocaiúva, s/n, Charitas, 24370-005</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6857,7 +6881,11 @@
           <t>Emergências psiquiátricas 24 horas</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2711-3166</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -6891,11 +6919,15 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Hospitais / RAPS</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
+          <t>SMS Niterói – Hospitais / RAPS; coordenadas/endereço: https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>-22.93253360899994</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>-43.09777747199997</v>
+      </c>
       <c r="P75" s="2" t="inlineStr"/>
       <c r="Q75" s="2" t="inlineStr">
         <is>
@@ -6909,7 +6941,7 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6958,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Avenida Prefeito Silvio Picanço, s/nº – Charitas</t>
+          <t>Avenida Carlos Ermelindo Marins, s/n, Jurujuba, 24370-005</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6934,7 +6966,11 @@
           <t>24 horas</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>3611-0107</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -6964,11 +7000,15 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Urgência e Emergência</t>
-        </is>
-      </c>
-      <c r="N76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
+          <t>SMS Niterói – Urgência e Emergência; coordenadas/endereço: https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>-22.93516314399995</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>-43.10094034799993</v>
+      </c>
       <c r="P76" s="2" t="inlineStr"/>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -6982,7 +7022,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7364,11 +7404,15 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Rua Clotilde de Oliveira Rodrigues, nº 42 – Fonseca</t>
+          <t>Rua Clotilde de Oliveira Rodrigues, 42, Fonseca, 24130-005</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>(21) 3613-2190 / (21) 97025-2769</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Norte I</t>
@@ -7398,11 +7442,15 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – Unidades de Saúde / RAPS</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
+          <t>SMS Niterói – Unidades de Saúde / RAPS; coordenadas/endereço: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>-22.88166784064276</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>-43.10576516987742</v>
+      </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
           <t>2293269</t>
@@ -7420,7 +7468,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7437,11 +7485,15 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Rua Joaquim Távora, nº 54 – São Francisco</t>
+          <t>Avenida Presidente Roosevelt, 465, São Francisco, 24310-410</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>(21)3613-2189 / (21)97031-4469</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Praias da Baía II</t>
@@ -7471,12 +7523,20 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
-      <c r="P83" s="2" t="inlineStr"/>
+          <t>SMS Niterói – RAPS; coordenadas/endereço: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>-22.9137152267681</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>-43.08412256434102</v>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2298856</t>
+        </is>
+      </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>Atenção psicossocial</t>
@@ -7489,7 +7549,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7566,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Rua Presidente Domiciano, nº 150 – São Domingos</t>
+          <t>Rua Dr. Fróes da Cruz, nº 22 – Centro, Niterói/RJ – CEP 24030-030</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7514,7 +7574,11 @@
           <t>24 horas</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>(21) 3613-2188 / (21) 97023-1678</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -7544,12 +7608,20 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
-      <c r="P84" s="2" t="inlineStr"/>
+          <t>https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>-22.88645631566079</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>-43.1242407886463</v>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>3296598</t>
+        </is>
+      </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>Atenção psicossocial</t>
@@ -7562,7 +7634,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7579,11 +7651,15 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Rua Ary Parreiras, nº 538 – Vital Brazil</t>
+          <t>Avenida Almirante Ary Parreiras, 649, Vital Brazil, 24230-321</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>(21) 3613-2192 / (21) 97026-9151</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Município de Niterói</t>
@@ -7613,12 +7689,20 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
-      <c r="P85" s="2" t="inlineStr"/>
+          <t>SMS Niterói – RAPS; coordenadas/endereço: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>-22.90436981561367</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>-43.09617793499951</v>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>3708330</t>
+        </is>
+      </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>Atenção psicossocial</t>
@@ -7631,7 +7715,7 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7648,11 +7732,15 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Rua Professor João Brasil, nº 1.000 – Fonseca</t>
+          <t>Rua Dr. Carlos Maximiano, 61, São Lourenço, 24120-000</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>(21) 3613-2191</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Norte I</t>
@@ -7682,11 +7770,15 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
+          <t>SMS Niterói – RAPS; coordenadas/endereço: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>-22.88288787141263</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>-43.10740882691125</v>
+      </c>
       <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
@@ -7700,7 +7792,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7786,11 +7878,15 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Endereço não publicado na página consultada</t>
+          <t>Avenida Almirante Ary Parreiras, 676, Vital Brazil, 24230-321</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>(21) 3613-2193 / (21) 97031-5406</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Praias da Baía II</t>
@@ -7820,11 +7916,15 @@
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
+          <t>SMS Niterói – RAPS; coordenadas/endereço: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>-22.90481339233579</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>-43.09557713671975</v>
+      </c>
       <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr">
         <is>
@@ -7838,7 +7938,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Coordenadas oficiais do SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7988,11 @@
           <t>Norte I</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Localizada no mesmo endereço do equipamento UBS Dr. Guilherme Taylor March; coordenada herdada do ponto oficial do SIG Niterói.</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
           <t>saudemental.prgtm@gmail.com</t>
@@ -7901,11 +8005,15 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
+          <t>SMS Niterói – RAPS; coordenada do equipamento co-localizado: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/Unidades_B%C3%A1sicas_de_Sa%C3%BAde_(UBS)_visualiza%C3%A7%C3%A3o/FeatureServer/0</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>-22.88667481309003</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>-43.08720458363261</v>
+      </c>
       <c r="P89" s="2" t="inlineStr"/>
       <c r="Q89" s="2" t="inlineStr">
         <is>
@@ -7919,7 +8027,7 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Co-localizado; coordenada oficial SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -7969,7 +8077,11 @@
           <t>Norte II</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Localizada no mesmo endereço do equipamento UBS Barreto; coordenada herdada do ponto oficial do SIG Niterói.</t>
+        </is>
+      </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>saudemental.eng@gmail.com</t>
@@ -7982,11 +8094,15 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SMS Niterói – RAPS</t>
-        </is>
-      </c>
-      <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
+          <t>SMS Niterói – RAPS; coordenada do equipamento co-localizado: https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/Unidades_B%C3%A1sicas_de_Sa%C3%BAde_(UBS)_visualiza%C3%A7%C3%A3o/FeatureServer/0</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>-22.86499749540229</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>-43.09958150357386</v>
+      </c>
       <c r="P90" s="2" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr">
         <is>
@@ -8000,7 +8116,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Localização pendente de validação</t>
+          <t>Co-localizado; coordenada oficial SIG Niterói</t>
         </is>
       </c>
     </row>
@@ -8945,7 +9061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9088,7 +9204,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Coordenadas SIG incluídas para 45 MMF, 11 UBS e 2 pontos SAMU. Nas demais linhas, latitude/longitude vazias indicam que a localização precisa não foi validada em camada oficial nesta consolidação.</t>
+          <t>72 registros têm coordenadas para exibição no mapa: 45 MMF, 11 UBS, 2 pontos SAMU, 6 pontos de equipamentos RAPS, 5 unidades municipais localizadas na camada SIGEO e 2 AASM co-localizados com UBS. Os outros 31 registros seguem sem coordenadas validadas; não aparecem como pontos no mapa até validação.</t>
         </is>
       </c>
     </row>
@@ -9125,6 +9241,66 @@
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Campo Região de Saúde segue os seis territórios da SMS/FMS. Conversão para as cinco regiões administrativas do mapa poderá ser feita por cruzamento espacial com a camada de bairros/regiões se for necessária para filtro territorial comum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coordenadas e cadastro da RAPS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://sig.niteroi.rj.gov.br/server/rest/services/Hosted/NGP_SMS_FESAUDE_P_RAPS_PUBLICO/FeatureServer/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Camada de hospitais do SIGEO (utilizada somente para as unidades municipais da planilha)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://services8.arcgis.com/TpaOLI1HCh5AcRQB/ArcGIS/rest/services/Grouplayer_SIGEO_AGOL/FeatureServer/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Atualização de coordenadas</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Em 01/10/2026 foram acrescentadas coordenadas oficiais da RAPS para CAPS AD III, CAPS II, CAPS i, Centro de Convivência e UAI; e do SIGEO para HGVF, HOF, HMCT, HPJ e Maternidade Municipal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AASM no Fonseca e no Barreto</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>As unidades aparecem nos mesmos endereços das UBS Dr. Guilherme Taylor March e UBS Barreto. Coordenadas herdadas dos pontos oficiais do SIG para as unidades co-localizadas; outros AASM continuam sem ponto validado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CAPS AD III Alcenir Veras</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Endereço, CNES, contato e coordenada obtidos na camada oficial da Rede de Atenção Psicossocial do SIG Niterói.</t>
         </is>
       </c>
     </row>
